--- a/docs/exports/bulgaria-real-estate-source-links.xlsx
+++ b/docs/exports/bulgaria-real-estate-source-links.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-07T14:19:20.112283+00:00</t>
+          <t>2026-04-08T11:04:29.800006+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/exports/bulgaria-real-estate-source-links.xlsx
+++ b/docs/exports/bulgaria-real-estate-source-links.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-08T11:04:29.800006+00:00</t>
+          <t>2026-04-08T14:33:00.857174+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/exports/bulgaria-real-estate-source-links.xlsx
+++ b/docs/exports/bulgaria-real-estate-source-links.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-08T14:33:00.857174+00:00</t>
+          <t>2026-04-29T03:47:34.205457+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/exports/bulgaria-real-estate-source-links.xlsx
+++ b/docs/exports/bulgaria-real-estate-source-links.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-04-29T03:47:34.205457+00:00</t>
+          <t>2026-04-29T08:12:29.213800+00:00</t>
         </is>
       </c>
     </row>
